--- a/Sajjad data/by_country_and_state/USA/IL.xlsx
+++ b/Sajjad data/by_country_and_state/USA/IL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="272">
   <si>
     <t>Business Name</t>
   </si>
@@ -764,6 +764,69 @@
   </si>
   <si>
     <t>2026-10-24T00:42:59.995Z</t>
+  </si>
+  <si>
+    <t>Total Health Dentistry-Dr. Jacquelyn Richardson</t>
+  </si>
+  <si>
+    <t>(309) 762-3015</t>
+  </si>
+  <si>
+    <t>609 35th Ave, Moline, IL 61265</t>
+  </si>
+  <si>
+    <t>Moline</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Total+Health+Dentistry-Dr.+Jacquelyn+Richardson/data=!4m7!3m6!1s0x87e2322bd71e8fe3:0x30ff59ffa17ad440!8m2!3d41.4753276!4d-90.5291859!16s%2Fg%2F1vfzfqlh!19sChIJ448e1ysy4ocRQNR6of9Z_zA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:10:49.453Z</t>
+  </si>
+  <si>
+    <t>Community Health Care - Rock Island Dental Clinic</t>
+  </si>
+  <si>
+    <t>(563) 327-2039</t>
+  </si>
+  <si>
+    <t>2750 11th St, Rock Island, IL 61201</t>
+  </si>
+  <si>
+    <t>Rock Island</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Community+Health+Care+-+Rock+Island+Dental+Clinic/data=!4m7!3m6!1s0x87e2332034b6b077:0x5db83e9513c3904a!8m2!3d41.4826319!4d-90.5835447!16s%2Fg%2F1tdhmcmn!19sChIJd7C2NCAz4ocRSpDDE5U-uF0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:10:51.576Z</t>
+  </si>
+  <si>
+    <t>White Guys Teeth Whitening Moline Quad Cities</t>
+  </si>
+  <si>
+    <t>(563) 265-1244</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>3625 27th St, Moline, IL 61265</t>
+  </si>
+  <si>
+    <t>SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/White+Guys+Teeth+Whitening+Moline+Quad+Cities/data=!4m7!3m6!1s0x87e235d408fb5b03:0x279185e8164f6c91!8m2!3d41.4758165!4d-90.4999071!16s%2Fg%2F1hc4p4g4w!19sChIJA1v7CNQ14ocRkWxPFuiFkSc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:11:38.585Z</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2801,6 +2864,129 @@
         <v>250</v>
       </c>
     </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>253</v>
+      </c>
+      <c r="E41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>255</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>256</v>
+      </c>
+      <c r="M41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>262</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>263</v>
+      </c>
+      <c r="M42" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" t="s">
+        <v>268</v>
+      </c>
+      <c r="E43" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>270</v>
+      </c>
+      <c r="M43" t="s">
+        <v>271</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
